--- a/artfynd/A 26136-2025 artfynd.xlsx
+++ b/artfynd/A 26136-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56826948</v>
+        <v>56826949</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>648227.1951360174</v>
+        <v>648227</v>
       </c>
       <c r="R2" t="n">
-        <v>7133396.139151143</v>
+        <v>7133396</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2015-05-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-10-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56826949</v>
+        <v>56826952</v>
       </c>
       <c r="B3" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>648227.1951360174</v>
+        <v>648251</v>
       </c>
       <c r="R3" t="n">
-        <v>7133396.139151143</v>
+        <v>7133553</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,19 +850,9 @@
           <t>2015-05-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-10-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,37 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73345076</v>
+        <v>73345075</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>648136.1188125445</v>
+        <v>648184</v>
       </c>
       <c r="R4" t="n">
-        <v>7133479.147227698</v>
+        <v>7133551</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,19 +957,9 @@
           <t>2018-09-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-09-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,15 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73345080</v>
+        <v>56826948</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,14 +1017,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åliden, Ås lm</t>
+          <t>Sör-Åliden, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>648139.0223950635</v>
+        <v>648227</v>
       </c>
       <c r="R5" t="n">
-        <v>7133464.068637269</v>
+        <v>7133396</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,22 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-09-21</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-09-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,66 +1067,71 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>73345077</v>
+        <v>56826951</v>
       </c>
       <c r="B6" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Åliden, Ås lm</t>
+          <t>Sör-Åliden, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>648136.1188125445</v>
+        <v>648251</v>
       </c>
       <c r="R6" t="n">
-        <v>7133479.147227698</v>
+        <v>7133553</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,22 +1158,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2018-09-21</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2018-09-21</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,53 +1174,58 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>73345079</v>
+        <v>73345065</v>
       </c>
       <c r="B7" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>648139.0223950635</v>
+        <v>648070</v>
       </c>
       <c r="R7" t="n">
-        <v>7133464.068637269</v>
+        <v>7133726</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,19 +1268,9 @@
           <t>2018-09-21</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2018-09-21</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,6 +1294,889 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>73345073</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Åliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>648184</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7133551</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Fredrika</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2018-09-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2018-09-21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>73345076</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Åliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>648136</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7133479</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Fredrika</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2018-09-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2018-09-21</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>73345080</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Åliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>648139</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7133464</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Fredrika</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2018-09-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2018-09-21</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>73345074</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Åliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>648184</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7133551</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Fredrika</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2018-09-21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2018-09-21</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>56826953</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sör-Åliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>648251</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7133553</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Fredrika</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2015-05-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2015-10-30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>73345077</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Åliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>648136</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7133479</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Fredrika</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2018-09-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2018-09-21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>73345079</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Åliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>648139</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7133464</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Fredrika</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2018-09-21</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2018-09-21</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>73345071</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Åliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>648184</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7133551</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Fredrika</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2018-09-21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2018-09-21</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>73345072</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Åliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>648184</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7133551</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Fredrika</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2018-09-21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2018-09-21</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Sören Uppsäll</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26136-2025 artfynd.xlsx
+++ b/artfynd/A 26136-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56826949</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56826952</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73345075</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56826948</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56826951</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73345065</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,6 +1426,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73345073</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73345076</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1585,6 +1630,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73345080</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73345074</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1789,6 +1844,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56826953</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1886,6 +1946,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73345077</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1983,6 +2048,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73345079</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2080,6 +2150,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73345071</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2177,8 +2252,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73345072</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>